--- a/PVA second supplier initiative/Quote_Comparison_Cardiac_MVR_Kit.xlsx
+++ b/PVA second supplier initiative/Quote_Comparison_Cardiac_MVR_Kit.xlsx
@@ -5,27 +5,30 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs &amp; Assumptions" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Head-to-Head @ 50" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Volume Curve" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Split Award" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Revision A0 to A1" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Scope &amp; Risk" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Process Comparison @ 50" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Volume Curve" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Split Award" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Revision A0 to A1" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Scope &amp; Risk" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Head-to-Head @ 50'!$A$1:$I$24</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Inputs &amp; Assumptions'!$A$1:$I$30</definedName>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Revision A0 to A1'!$A$1:$G$16</definedName>
-    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">'Scope &amp; Risk'!$A$1:$D$25</definedName>
-    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Split Award'!$A$1:$H$21</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Volume Curve'!$A$1:$H$45</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Process Comparison @ 50'!$A$1:$H$26</definedName>
+    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">'Revision A0 to A1'!$A$1:$G$16</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Scope &amp; Risk'!$A$1:$D$25</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Split Award'!$A$1:$H$21</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Volume Curve'!$A$1:$H$45</definedName>
     <definedName function="false" hidden="false" name="KitA0" vbProcedure="false">'Inputs &amp; Assumptions'!$D$21</definedName>
     <definedName function="false" hidden="false" name="KitA1q1" vbProcedure="false">'Inputs &amp; Assumptions'!$E$21</definedName>
     <definedName function="false" hidden="false" name="KitA1q20" vbProcedure="false">'Inputs &amp; Assumptions'!$F$21</definedName>
     <definedName function="false" hidden="false" name="KitA1q50" vbProcedure="false">'Inputs &amp; Assumptions'!$G$21</definedName>
+    <definedName function="false" hidden="false" name="KitFsls" vbProcedure="false">'Inputs &amp; Assumptions'!$I$21</definedName>
     <definedName function="false" hidden="false" name="KitX50" vbProcedure="false">'Inputs &amp; Assumptions'!$H$21</definedName>
     <definedName function="false" hidden="false" name="QtyKits" vbProcedure="false">'Inputs &amp; Assumptions'!$C$30</definedName>
     <definedName function="false" hidden="false" name="VolKit" vbProcedure="false">'Inputs &amp; Assumptions'!$C$21</definedName>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="220">
   <si>
     <t xml:space="preserve">Quote Comparison — Cardiac MVR Suture Skills Kit (3 parts)</t>
   </si>
@@ -62,6 +65,10 @@
     <t xml:space="preserve">Xometry</t>
   </si>
   <si>
+    <t xml:space="preserve">Fictiv A2 — SLS
+(newest)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quote reference</t>
   </si>
   <si>
@@ -86,6 +93,9 @@
     <t xml:space="preserve">2025-11-24</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fictiv A1 supersedes A0 three days later. Xometry is ~9 months old.</t>
   </si>
   <si>
@@ -101,6 +111,9 @@
     <t xml:space="preserve">2025-12-24</t>
   </si>
   <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
     <t xml:space="preserve">Xometry's 30-day price honour lapsed long ago — treat as indicative.</t>
   </si>
   <si>
@@ -140,6 +153,9 @@
     <t xml:space="preserve">Nylon 12</t>
   </si>
   <si>
+    <t xml:space="preserve">Nylon (powder)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chemically equivalent.</t>
   </si>
   <si>
@@ -159,6 +175,9 @@
   </si>
   <si>
     <t xml:space="preserve">Included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/14/13-pt</t>
   </si>
   <si>
     <t xml:space="preserve">Xometry carries dimensional report + 5 FAI. Fictiv does not.</t>
@@ -194,6 +213,10 @@
 @ qty 50</t>
   </si>
   <si>
+    <t xml:space="preserve">Fictiv SLS
+@ qty 50</t>
+  </si>
+  <si>
     <t xml:space="preserve">667357  Valve receptacle</t>
   </si>
   <si>
@@ -222,6 +245,9 @@
   </si>
   <si>
     <t xml:space="preserve">EDIT ME. 50 is the only quantity both vendors have quoted. At 1 or 20 only Fictiv has a price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUOTE 4 (Fictiv, SLS): printed QUOTE TOTAL is $74,616.29 but the three line items sum to $67,364.00. The $7,252.29 difference is not itemised on the page supplied and is EXCLUDED from every parts-only comparison in this workbook. Confirm with Fictiv what it covers before comparing totals.</t>
   </si>
   <si>
     <t xml:space="preserve">Like-for-Like: Both Vendors at Quantity 50</t>
@@ -301,6 +327,96 @@
   </si>
   <si>
     <t xml:space="preserve">HEADLINE: Xometry still wins the kit at qty 50, but by 36% rather than the 63% the first comparison suggested. Fictiv is now CHEAPER on 667357 (valve receptacle) — the first part where it beats Xometry. The remaining gap is concentrated entirely in the two large parts (chest and base), where Fictiv is ~38% more expensive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three Options at Quantity 50 — MJF vs SLS vs Xometry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv re-quoted the same three parts on SLS. The process switch cut its price 21.5% and closed most of the gap to Xometry. Parts only — Fictiv's quote total carries $7,252.29 that Xometry has not quoted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv MJF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MJF→SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xometry SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheapest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small part packs ~117 per MJF build — no envelope penalty, so MJF wins it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large hollow shell: only ~2 per MJF build vs ~12 on large-format SLS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Largest part — biggest envelope penalty on MJF, so the biggest SLS gain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT (one of each)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL AT 50 KITS  (parts only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv — MJF (superseded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv — SLS (newest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xometry — SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saved by switching MJF→SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What the process change alone bought.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remaining gap to Xometry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was $31,287 on MJF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remaining gap (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was 36.5% on MJF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEST ACHIEVABLE MIXES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Split award — cheapest vendor per part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">667357 from Fictiv MJF, the two large parts from Xometry. Saves only ~$294 (0.5%) over all-Xometry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best all-Fictiv mix (MJF + SLS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valve on MJF, chest and base on SLS. $911 under Fictiv's all-SLS quote — ask for it as one order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All-Xometry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The benchmark this comparison is measured against.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECHANISM: powder-bed cost tracks parts-per-build. The two large parts are ~10-litre bounding boxes only 2-4% filled; MJF's 41 L chamber takes ~2 of them per build against ~9-12 on a large-format SLS machine (154 L). That is why SLS helped the big parts and HURT the small one (+33.9%). Machine classes are inferred from the quoted processes — neither vendor names its equipment.</t>
   </si>
   <si>
     <t xml:space="preserve">How Fictiv's Price Moves With Quantity</t>
@@ -607,16 +723,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="\$#,##0"/>
-    <numFmt numFmtId="170" formatCode="0.00%"/>
+    <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="\$#,##0"/>
+    <numFmt numFmtId="171" formatCode="\$#,##0"/>
+    <numFmt numFmtId="172" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -719,6 +837,14 @@
       <b val="true"/>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF375623"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -918,7 +1044,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -963,6 +1089,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -975,11 +1105,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -987,7 +1121,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -995,83 +1129,123 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1084,7 +1258,22 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF006100"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -1411,11 +1600,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="39590273"/>
-        <c:axId val="76428286"/>
+        <c:axId val="52827910"/>
+        <c:axId val="78321867"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="39590273"/>
+        <c:axId val="52827910"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1480,7 +1669,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76428286"/>
+        <c:crossAx val="78321867"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1488,7 +1677,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76428286"/>
+        <c:axId val="78321867"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1553,7 +1742,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39590273"/>
+        <c:crossAx val="52827910"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1616,9 +1805,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>249840</xdr:colOff>
+      <xdr:colOff>249480</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>47160</xdr:rowOff>
+      <xdr:rowOff>46800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1627,7 +1816,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="177840" y="5172120"/>
-        <a:ext cx="5939280" cy="3095280"/>
+        <a:ext cx="5938920" cy="3094920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1820,14 +2009,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:I30"/>
+  <dimension ref="B2:J34"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="58"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1870,174 +2060,200 @@
       <c r="E6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="3"/>
+      <c r="F8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="8"/>
+        <v>26</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -2049,31 +2265,33 @@
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>2.56</v>
@@ -2093,10 +2311,13 @@
       <c r="H18" s="10" t="n">
         <v>59.58</v>
       </c>
+      <c r="I18" s="11" t="n">
+        <v>71.93</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>11.952</v>
@@ -2116,10 +2337,13 @@
       <c r="H19" s="10" t="n">
         <v>378.56</v>
       </c>
+      <c r="I19" s="11" t="n">
+        <v>541.58</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>25.007</v>
@@ -2139,39 +2363,46 @@
       <c r="H20" s="10" t="n">
         <v>652.66</v>
       </c>
+      <c r="I20" s="11" t="n">
+        <v>733.77</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="12" t="n">
+      <c r="B21" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="13" t="n">
         <f aca="false">SUM(C18:C20)</f>
         <v>39.519</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="14" t="n">
         <f aca="false">SUM(D18:D20)</f>
         <v>2917.56</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="14" t="n">
         <f aca="false">SUM(E18:E20)</f>
         <v>2764</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="14" t="n">
         <f aca="false">SUM(F18:F20)</f>
         <v>1808.11</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="14" t="n">
         <f aca="false">SUM(G18:G20)</f>
         <v>1716.54</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="H21" s="14" t="n">
         <f aca="false">SUM(H18:H20)</f>
         <v>1090.8</v>
       </c>
+      <c r="I21" s="15" t="n">
+        <f aca="false">SUM(I18:I20)</f>
+        <v>1347.28</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -2185,40 +2416,40 @@
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="D25" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="F25" s="14" t="n">
+      <c r="F25" s="16" t="n">
         <v>32</v>
       </c>
-      <c r="G25" s="14" t="n">
+      <c r="G25" s="16" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -2240,7 +2471,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -2252,32 +2483,68 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="C30" s="17" t="n">
         <v>50</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
     </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="G14:J14"/>
     <mergeCell ref="B26:I27"/>
     <mergeCell ref="E30:I30"/>
+    <mergeCell ref="B32:J34"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
@@ -2308,12 +2575,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -2325,168 +2592,168 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="16" t="str">
+      <c r="B6" s="18" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B18</f>
         <v>667357  Valve receptacle</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!G18</f>
         <v>53.71</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!H18</f>
         <v>59.58</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <f aca="false">C6-D6</f>
         <v>-5.87</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="19" t="n">
         <f aca="false">IF(MAX(C6,D6)=0,0,ABS(C6-D6)/MAX(C6,D6))</f>
         <v>0.098522994293387</v>
       </c>
-      <c r="G6" s="18" t="str">
+      <c r="G6" s="20" t="str">
         <f aca="false">IF(C6&lt;D6,"FICTIV","XOMETRY")</f>
         <v>FICTIV</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="14" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!C18=0,0,C6/'Inputs &amp; Assumptions'!C18)</f>
         <v>20.98046875</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="I6" s="14" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!C18=0,0,D6/'Inputs &amp; Assumptions'!C18)</f>
         <v>23.2734375</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="16" t="str">
+      <c r="B7" s="18" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B19</f>
         <v>667355  Chest</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!G19</f>
         <v>616.18</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!H19</f>
         <v>378.56</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <f aca="false">C7-D7</f>
         <v>237.62</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="19" t="n">
         <f aca="false">IF(MAX(C7,D7)=0,0,ABS(C7-D7)/MAX(C7,D7))</f>
         <v>0.385634067967152</v>
       </c>
-      <c r="G7" s="18" t="str">
+      <c r="G7" s="20" t="str">
         <f aca="false">IF(C7&lt;D7,"FICTIV","XOMETRY")</f>
         <v>XOMETRY</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="14" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!C19=0,0,C7/'Inputs &amp; Assumptions'!C19)</f>
         <v>51.5545515394913</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I7" s="14" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!C19=0,0,D7/'Inputs &amp; Assumptions'!C19)</f>
         <v>31.673360107095</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="16" t="str">
+      <c r="B8" s="18" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B20</f>
         <v>667354  Base</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!G20</f>
         <v>1046.65</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!H20</f>
         <v>652.66</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <f aca="false">C8-D8</f>
         <v>393.99</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="19" t="n">
         <f aca="false">IF(MAX(C8,D8)=0,0,ABS(C8-D8)/MAX(C8,D8))</f>
         <v>0.376429560980271</v>
       </c>
-      <c r="G8" s="18" t="str">
+      <c r="G8" s="20" t="str">
         <f aca="false">IF(C8&lt;D8,"FICTIV","XOMETRY")</f>
         <v>XOMETRY</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="14" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!C20=0,0,C8/'Inputs &amp; Assumptions'!C20)</f>
         <v>41.8542808013756</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="I8" s="14" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!C20=0,0,D8/'Inputs &amp; Assumptions'!C20)</f>
         <v>26.0990922541688</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="13" t="n">
+      <c r="B9" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="14" t="n">
         <f aca="false">SUM(C6:C8)</f>
         <v>1716.54</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <f aca="false">SUM(D6:D8)</f>
         <v>1090.8</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <f aca="false">C9-D9</f>
         <v>625.74</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="19" t="n">
         <f aca="false">IF(MAX(C9,D9)=0,0,ABS(C9-D9)/MAX(C9,D9))</f>
         <v>0.364535635639135</v>
       </c>
-      <c r="G9" s="18" t="str">
+      <c r="G9" s="20" t="str">
         <f aca="false">IF(C9&lt;D9,"FICTIV","XOMETRY")</f>
         <v>XOMETRY</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="14" t="n">
         <f aca="false">IF(VolKit=0,0,C9/VolKit)</f>
         <v>43.4358156835952</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I9" s="14" t="n">
         <f aca="false">IF(VolKit=0,0,D9/VolKit)</f>
         <v>27.6019130038716</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -2497,43 +2764,43 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="19" t="n">
+        <v>76</v>
+      </c>
+      <c r="C12" s="21" t="n">
         <f aca="false">C9*QtyKits</f>
         <v>85827</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="19" t="n">
+        <v>77</v>
+      </c>
+      <c r="C13" s="21" t="n">
         <f aca="false">D9*QtyKits</f>
         <v>54540</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="20" t="n">
+        <v>78</v>
+      </c>
+      <c r="C14" s="22" t="n">
         <f aca="false">C12-C13</f>
         <v>31287</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="C15" s="19" t="n">
         <f aca="false">IF(C12=0,0,(C12-C13)/C12)</f>
         <v>0.364535635639135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -2544,14 +2811,14 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="17" t="n">
+        <v>81</v>
+      </c>
+      <c r="C18" s="19" t="n">
         <f aca="false">IF(KitA0=0,0,1-KitX50/KitA0)</f>
         <v>0.626125940854687</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -2561,14 +2828,14 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="17" t="n">
+        <v>83</v>
+      </c>
+      <c r="C19" s="19" t="n">
         <f aca="false">IF(C9=0,0,1-D9/C9)</f>
         <v>0.364535635639135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -2578,14 +2845,14 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="C20" s="19" t="n">
         <f aca="false">IF(KitA1q1=0,0,1-KitA1q50/KitA1q1)</f>
         <v>0.378965267727931</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -2595,14 +2862,14 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="17" t="n">
+        <v>87</v>
+      </c>
+      <c r="C21" s="19" t="n">
         <f aca="false">IF(KitA1q1=0,0,1-KitX50/KitA1q1)</f>
         <v>0.605354558610709</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -2612,7 +2879,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="8" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -2661,6 +2928,367 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
+  <dimension ref="B2:H26"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="24" t="str">
+        <f aca="false">'Inputs &amp; Assumptions'!B18</f>
+        <v>667357  Valve receptacle</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <f aca="false">'Inputs &amp; Assumptions'!G18</f>
+        <v>53.71</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <f aca="false">'Inputs &amp; Assumptions'!I18</f>
+        <v>71.93</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <f aca="false">IF(C6=0,0,D6/C6-1)</f>
+        <v>0.339229193818656</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <f aca="false">'Inputs &amp; Assumptions'!H18</f>
+        <v>59.58</v>
+      </c>
+      <c r="G6" s="20" t="str">
+        <f aca="false">IF(MIN(C6,D6,F6)=C6,"Fictiv MJF",IF(MIN(C6,D6,F6)=D6,"Fictiv SLS","Xometry"))</f>
+        <v>Fictiv MJF</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="24" t="str">
+        <f aca="false">'Inputs &amp; Assumptions'!B19</f>
+        <v>667355  Chest</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <f aca="false">'Inputs &amp; Assumptions'!G19</f>
+        <v>616.18</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <f aca="false">'Inputs &amp; Assumptions'!I19</f>
+        <v>541.58</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <f aca="false">IF(C7=0,0,D7/C7-1)</f>
+        <v>-0.121068518939271</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <f aca="false">'Inputs &amp; Assumptions'!H19</f>
+        <v>378.56</v>
+      </c>
+      <c r="G7" s="20" t="str">
+        <f aca="false">IF(MIN(C7,D7,F7)=C7,"Fictiv MJF",IF(MIN(C7,D7,F7)=D7,"Fictiv SLS","Xometry"))</f>
+        <v>Xometry</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="24" t="str">
+        <f aca="false">'Inputs &amp; Assumptions'!B20</f>
+        <v>667354  Base</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <f aca="false">'Inputs &amp; Assumptions'!G20</f>
+        <v>1046.65</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <f aca="false">'Inputs &amp; Assumptions'!I20</f>
+        <v>733.77</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <f aca="false">IF(C8=0,0,D8/C8-1)</f>
+        <v>-0.298934696412363</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <f aca="false">'Inputs &amp; Assumptions'!H20</f>
+        <v>652.66</v>
+      </c>
+      <c r="G8" s="20" t="str">
+        <f aca="false">IF(MIN(C8,D8,F8)=C8,"Fictiv MJF",IF(MIN(C8,D8,F8)=D8,"Fictiv SLS","Xometry"))</f>
+        <v>Xometry</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <f aca="false">SUM(C6:C8)</f>
+        <v>1716.54</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <f aca="false">SUM(D6:D8)</f>
+        <v>1347.28</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <f aca="false">IF(C9=0,0,D9/C9-1)</f>
+        <v>-0.215118785463782</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <f aca="false">SUM(F6:F8)</f>
+        <v>1090.8</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <f aca="false">C9*QtyKits</f>
+        <v>85827</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <f aca="false">D9*QtyKits</f>
+        <v>67364</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <f aca="false">F9*QtyKits</f>
+        <v>54540</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <f aca="false">C12-C13</f>
+        <v>18463</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="32" t="n">
+        <f aca="false">C13-C14</f>
+        <v>12824</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <f aca="false">IF(C13=0,0,(C13-C14)/C13)</f>
+        <v>0.190368742948756</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <f aca="false">(MIN(C6,D6,F6)+MIN(C7,D7,F7)+MIN(C8,D8,F8))*QtyKits</f>
+        <v>54246.5</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <f aca="false">(MIN(C6,D6)+MIN(C7,D7)+MIN(C8,D8))*QtyKits</f>
+        <v>66453</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="30" t="n">
+        <f aca="false">F9*QtyKits</f>
+        <v>54540</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="B24:H26"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C6:F9">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>MIN($C6,$D6,$F6)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;A&amp;RPage &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="B2:M26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -2672,12 +3300,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -2687,126 +3315,126 @@
       <c r="H3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K4" s="21" t="s">
-        <v>85</v>
+      <c r="K4" s="33" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-      <c r="K5" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="M5" s="22" t="s">
-        <v>89</v>
+      <c r="K5" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="M5" s="34" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="K6" s="23" t="n">
+      <c r="K6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="24" t="n">
+      <c r="L6" s="36" t="n">
         <f aca="false">KitA1q1</f>
         <v>2764</v>
       </c>
-      <c r="M6" s="24" t="n">
+      <c r="M6" s="36" t="n">
         <f aca="false">KitX50</f>
         <v>1090.8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="13" t="n">
+        <v>130</v>
+      </c>
+      <c r="C7" s="14" t="n">
         <f aca="false">KitA1q1</f>
         <v>2764</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <f aca="false">KitA1q20</f>
         <v>1808.11</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <f aca="false">KitA1q50</f>
         <v>1716.54</v>
       </c>
-      <c r="K7" s="23" t="n">
+      <c r="K7" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="L7" s="24" t="n">
+      <c r="L7" s="36" t="n">
         <f aca="false">KitA1q20</f>
         <v>1808.11</v>
       </c>
-      <c r="M7" s="24" t="n">
+      <c r="M7" s="36" t="n">
         <f aca="false">KitX50</f>
         <v>1090.8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="13" t="n">
+        <v>131</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" s="14" t="n">
         <f aca="false">KitX50</f>
         <v>1090.8</v>
       </c>
-      <c r="K8" s="23" t="n">
+      <c r="K8" s="35" t="n">
         <v>50</v>
       </c>
-      <c r="L8" s="24" t="n">
+      <c r="L8" s="36" t="n">
         <f aca="false">KitA1q50</f>
         <v>1716.54</v>
       </c>
-      <c r="M8" s="24" t="n">
+      <c r="M8" s="36" t="n">
         <f aca="false">KitX50</f>
         <v>1090.8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" s="17" t="n">
+        <v>133</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="19" t="n">
         <f aca="false">IF(KitX50=0,0,KitA1q50/KitX50-1)</f>
         <v>0.573652365236524</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -2816,94 +3444,94 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="16" t="str">
+      <c r="B13" s="18" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B18</f>
         <v>667357  Valve receptacle</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="19" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!E18=0,0,'Inputs &amp; Assumptions'!F18/'Inputs &amp; Assumptions'!E18-1)</f>
         <v>-0.633667083854819</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="19" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!F18=0,0,'Inputs &amp; Assumptions'!G18/'Inputs &amp; Assumptions'!F18-1)</f>
         <v>-0.0825076870515886</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="19" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!E18=0,0,'Inputs &amp; Assumptions'!G18/'Inputs &amp; Assumptions'!E18-1)</f>
         <v>-0.663892365456821</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="16" t="str">
+      <c r="B14" s="18" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B19</f>
         <v>667355  Chest</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="19" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!E19=0,0,'Inputs &amp; Assumptions'!F19/'Inputs &amp; Assumptions'!E19-1)</f>
         <v>-0.341358363300217</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="19" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!F19=0,0,'Inputs &amp; Assumptions'!G19/'Inputs &amp; Assumptions'!F19-1)</f>
         <v>-0.0496622351090411</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="19" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!E19=0,0,'Inputs &amp; Assumptions'!G19/'Inputs &amp; Assumptions'!E19-1)</f>
         <v>-0.374067979114606</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="16" t="str">
+      <c r="B15" s="18" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B20</f>
         <v>667354  Base</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="19" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!E20=0,0,'Inputs &amp; Assumptions'!F20/'Inputs &amp; Assumptions'!E20-1)</f>
         <v>-0.320160762572695</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="19" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!F20=0,0,'Inputs &amp; Assumptions'!G20/'Inputs &amp; Assumptions'!F20-1)</f>
         <v>-0.0495282376338324</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="19" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!E20=0,0,'Inputs &amp; Assumptions'!G20/'Inputs &amp; Assumptions'!E20-1)</f>
         <v>-0.353832001876798</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="17" t="n">
+      <c r="B16" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="19" t="n">
         <f aca="false">IF(KitA1q1=0,0,KitA1q20/KitA1q1-1)</f>
         <v>-0.345835745296672</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="19" t="n">
         <f aca="false">IF(KitA1q20=0,0,KitA1q50/KitA1q20-1)</f>
         <v>-0.0506440426743949</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="19" t="n">
         <f aca="false">IF(KitA1q1=0,0,KitA1q50/KitA1q1-1)</f>
         <v>-0.378965267727931</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="8" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -2923,7 +3551,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -2933,45 +3561,45 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C22" s="13" t="n">
+        <v>141</v>
+      </c>
+      <c r="C22" s="14" t="n">
         <f aca="false">KitA1q50</f>
         <v>1716.54</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="13" t="n">
+        <v>142</v>
+      </c>
+      <c r="C23" s="14" t="n">
         <f aca="false">KitX50</f>
         <v>1090.8</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C24" s="26" t="n">
+        <v>143</v>
+      </c>
+      <c r="C24" s="38" t="n">
         <f aca="false">IF(KitA1q50=0,0,1-KitX50/KitA1q50)</f>
         <v>0.364535635639135</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="13" t="n">
+        <v>144</v>
+      </c>
+      <c r="C25" s="14" t="n">
         <f aca="false">KitA1q50-KitX50</f>
         <v>625.74</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C26" s="19" t="n">
+        <v>145</v>
+      </c>
+      <c r="C26" s="21" t="n">
         <f aca="false">(KitA1q50-KitX50)*QtyKits</f>
         <v>31287</v>
       </c>
@@ -2992,7 +3620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -3010,12 +3638,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -3026,119 +3654,119 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="H5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="16" t="str">
+      <c r="B6" s="18" t="str">
         <f aca="false">'Head-to-Head @ 50'!B6</f>
         <v>667357  Valve receptacle</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <f aca="false">'Head-to-Head @ 50'!C6</f>
         <v>53.71</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <f aca="false">'Head-to-Head @ 50'!D6</f>
         <v>59.58</v>
       </c>
-      <c r="E6" s="18" t="str">
+      <c r="E6" s="20" t="str">
         <f aca="false">IF(C6&lt;D6,"FICTIV","XOMETRY")</f>
         <v>FICTIV</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="14" t="n">
         <f aca="false">MIN(C6,D6)</f>
         <v>53.71</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="21" t="n">
         <f aca="false">F6*QtyKits</f>
         <v>2685.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="16" t="str">
+      <c r="B7" s="18" t="str">
         <f aca="false">'Head-to-Head @ 50'!B7</f>
         <v>667355  Chest</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <f aca="false">'Head-to-Head @ 50'!C7</f>
         <v>616.18</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <f aca="false">'Head-to-Head @ 50'!D7</f>
         <v>378.56</v>
       </c>
-      <c r="E7" s="18" t="str">
+      <c r="E7" s="20" t="str">
         <f aca="false">IF(C7&lt;D7,"FICTIV","XOMETRY")</f>
         <v>XOMETRY</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="14" t="n">
         <f aca="false">MIN(C7,D7)</f>
         <v>378.56</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="21" t="n">
         <f aca="false">F7*QtyKits</f>
         <v>18928</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="16" t="str">
+      <c r="B8" s="18" t="str">
         <f aca="false">'Head-to-Head @ 50'!B8</f>
         <v>667354  Base</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <f aca="false">'Head-to-Head @ 50'!C8</f>
         <v>1046.65</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <f aca="false">'Head-to-Head @ 50'!D8</f>
         <v>652.66</v>
       </c>
-      <c r="E8" s="18" t="str">
+      <c r="E8" s="20" t="str">
         <f aca="false">IF(C8&lt;D8,"FICTIV","XOMETRY")</f>
         <v>XOMETRY</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <f aca="false">MIN(C8,D8)</f>
         <v>652.66</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="21" t="n">
         <f aca="false">F8*QtyKits</f>
         <v>32633</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="F9" s="13" t="n">
+      <c r="B9" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" s="14" t="n">
         <f aca="false">SUM(F6:F8)</f>
         <v>1084.93</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="21" t="n">
         <f aca="false">SUM(G6:G8)</f>
         <v>54246.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -3148,41 +3776,41 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="19" t="n">
+        <v>155</v>
+      </c>
+      <c r="C12" s="21" t="n">
         <f aca="false">KitX50*QtyKits</f>
         <v>54540</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" s="19" t="n">
+        <v>156</v>
+      </c>
+      <c r="C13" s="21" t="n">
         <f aca="false">KitA1q50*QtyKits</f>
         <v>85827</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" s="19" t="n">
+        <v>157</v>
+      </c>
+      <c r="C14" s="21" t="n">
         <f aca="false">G9</f>
         <v>54246.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" s="27" t="n">
+        <v>158</v>
+      </c>
+      <c r="C15" s="39" t="n">
         <f aca="false">C12-C14</f>
         <v>293.5</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -3191,14 +3819,14 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="17" t="n">
+        <v>160</v>
+      </c>
+      <c r="C16" s="19" t="n">
         <f aca="false">IF(C12=0,0,(C12-C14)/C12)</f>
         <v>0.00538137147048038</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -3207,14 +3835,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="19" t="n">
+        <v>162</v>
+      </c>
+      <c r="C17" s="21" t="n">
         <f aca="false">C13-C14</f>
         <v>31580.5</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -3223,7 +3851,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="8" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -3273,7 +3901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -3290,12 +3918,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -3305,112 +3933,112 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="16" t="str">
+      <c r="B6" s="18" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B18</f>
         <v>667357  Valve receptacle</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!D18</f>
         <v>168.68</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!E18</f>
         <v>159.8</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <f aca="false">D6-C6</f>
         <v>-8.88</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="40" t="n">
         <f aca="false">IF(C6=0,0,D6/C6-1)</f>
         <v>-0.0526440597581218</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="16" t="str">
+      <c r="B7" s="18" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B19</f>
         <v>667355  Chest</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!D19</f>
         <v>1039.11</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!E19</f>
         <v>984.42</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <f aca="false">D7-C7</f>
         <v>-54.6899999999999</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="40" t="n">
         <f aca="false">IF(C7=0,0,D7/C7-1)</f>
         <v>-0.0526315789473684</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="16" t="str">
+      <c r="B8" s="18" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B20</f>
         <v>667354  Base</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!D20</f>
         <v>1709.77</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!E20</f>
         <v>1619.78</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <f aca="false">D8-C8</f>
         <v>-89.99</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="40" t="n">
         <f aca="false">IF(C8=0,0,D8/C8-1)</f>
         <v>-0.0526328102610293</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="13" t="n">
+      <c r="B9" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="14" t="n">
         <f aca="false">SUM(C6:C8)</f>
         <v>2917.56</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <f aca="false">SUM(D6:D8)</f>
         <v>2764</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <f aca="false">D9-C9</f>
         <v>-153.56</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="40" t="n">
         <f aca="false">IF(C9=0,0,D9/C9-1)</f>
         <v>-0.0526330221143695</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -3418,40 +4046,40 @@
       <c r="F11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
+      <c r="B12" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="B13" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="B14" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3470,7 +4098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -3486,190 +4114,190 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="31"/>
+      <c r="B6" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" s="43"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="29" t="s">
-        <v>146</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="31"/>
+      <c r="B7" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="43"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="D8" s="31"/>
+      <c r="B8" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="43"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="D9" s="31"/>
+      <c r="B9" s="41" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="D9" s="43"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="D10" s="31"/>
+      <c r="B10" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" s="43"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="D11" s="31"/>
+      <c r="B11" s="41" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" s="43"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>161</v>
+      <c r="B14" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="D15" s="35" t="s">
-        <v>164</v>
+      <c r="B15" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="D16" s="36" t="s">
-        <v>167</v>
+      <c r="B16" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>170</v>
+      <c r="B17" s="44" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="D17" s="49" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>173</v>
+      <c r="B18" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>209</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>161</v>
+      <c r="B19" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>212</v>
+      </c>
+      <c r="D19" s="46" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="D20" s="34" t="s">
-        <v>161</v>
+      <c r="B20" s="44" t="s">
+        <v>213</v>
+      </c>
+      <c r="C20" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="D20" s="46" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="C21" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="D21" s="37" t="s">
-        <v>170</v>
+      <c r="B21" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="C21" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="D21" s="49" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>170</v>
+      <c r="B22" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="C22" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="3" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>

--- a/PVA second supplier initiative/Quote_Comparison_Cardiac_MVR_Kit.xlsx
+++ b/PVA second supplier initiative/Quote_Comparison_Cardiac_MVR_Kit.xlsx
@@ -5,25 +5,27 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Inputs &amp; Assumptions" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Head-to-Head @ 50" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Process Comparison @ 50" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Volume Curve" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Split Award" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Revision A0 to A1" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Scope &amp; Risk" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Inputs &amp; Assumptions" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Head-to-Head @ 50" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Process Comparison @ 50" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Volume Curve" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Split Award" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Revision A0 to A1" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Scope &amp; Risk" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Head-to-Head @ 50'!$A$1:$I$24</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Inputs &amp; Assumptions'!$A$1:$I$30</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Process Comparison @ 50'!$A$1:$H$26</definedName>
-    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">'Revision A0 to A1'!$A$1:$G$16</definedName>
-    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Scope &amp; Risk'!$A$1:$D$25</definedName>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Split Award'!$A$1:$H$21</definedName>
-    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Volume Curve'!$A$1:$H$45</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$A$1:$I$51</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Head-to-Head @ 50'!$A$1:$I$24</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Inputs &amp; Assumptions'!$A$1:$I$30</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Process Comparison @ 50'!$A$1:$H$26</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Revision A0 to A1'!$A$1:$G$16</definedName>
+    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Scope &amp; Risk'!$A$1:$D$25</definedName>
+    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">'Split Award'!$A$1:$H$21</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Volume Curve'!$A$1:$H$45</definedName>
     <definedName function="false" hidden="false" name="KitA0" vbProcedure="false">'Inputs &amp; Assumptions'!$D$21</definedName>
     <definedName function="false" hidden="false" name="KitA1q1" vbProcedure="false">'Inputs &amp; Assumptions'!$E$21</definedName>
     <definedName function="false" hidden="false" name="KitA1q20" vbProcedure="false">'Inputs &amp; Assumptions'!$F$21</definedName>
@@ -43,7 +45,289 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="297">
+  <si>
+    <t xml:space="preserve">Cardiac MVR Suture Skills Kit — Sourcing Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three parts, quantity 50. Four quotes, two vendors. Fictiv's SLS re-quote cut its price 21.5% and closed most of the gap, but Xometry still holds the lowest parts cost. Every figure is PARTS ONLY — Xometry has never quoted shipping or tax. Live formulas; all detail sheets sit behind this one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT A GLANCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOWEST PARTS COST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP TO FICTIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAVED BY MJF → SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNEXPLAINED ON FICTIV TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xometry, SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0% — was $31,287 on MJF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv cut 21.5% on process alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote total $74,616.29 vs parts $67,364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL PARTS COST — 50 KITS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total @ 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per kit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs cheapest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Split award (best per part)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MJF + SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xometry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 business days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv — best mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 production days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv — all SLS (newest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv — MJF (superseded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MJF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 production days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The split award saves only ~$294 (0.5%) over single-sourcing Xometry — not worth two suppliers on price alone. Fictiv's own best mix (MJF for the valve, SLS for the other two) is $911 under its all-SLS quote: worth asking for as one order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHERE THE MONEY IS — UNIT PRICE AT QTY 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv MJF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MJF → SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xometry SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheapest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packs ~117 per MJF build — no envelope penalty, so MJF wins it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large hollow shell: ~2 per MJF build vs ~12 on large-format SLS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Largest part, biggest MJF envelope penalty — biggest SLS gain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT (one of each)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARE THEY QUOTING THE SAME THING?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criterion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv — SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xometry — SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selective Laser Sintering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nylon (powder)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nylon 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black / White / Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black-dyed / Natural / Black-dyed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-pt, 14-pt, 13-pt dimensional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dimensional report + 5 first articles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close, not identical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 business days, after FAI acceptance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv faster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chest drawing revision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rev_c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REV B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Different geometry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 months; price honour lapsed Dec 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xometry stale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping &amp; tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inside the $74,616.29 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculated at checkout — never quoted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not comparable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEFORE YOU AWARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why it matters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask Fictiv to itemise the $7,252.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote total $74,616.29 vs line items $67,364.00 — 10.8% of the quote, and more than half the remaining gap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask Xometry to re-quote on current pricing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The $54,540 that wins this comparison was quoted Nov 2025; its 30-day price honour lapsed in Dec.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settle the chest drawing revision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictiv quoted rev_c, Xometry REV B — different geometry on a part carrying $27,079 of the order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level the inspection scope on both sides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xometry ships 5 first articles; Fictiv names point-counts only. Price the same plan both ways.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask Fictiv for the MJF + SLS mix as one order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MJF for the valve, SLS for the other two: $66,453, i.e. $911 under its all-SLS quote.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basis: parts-only cost at quantity 50, from four quote documents. Every extended price reproduces from its own unit price x quantity, and each quote's printed total reproduces from the model. Build-packing figures behind the 'Why' column are modelled from part envelopes against published machine build volumes — neither vendor names its equipment. No personal data is carried into this workbook.</t>
+  </si>
   <si>
     <t xml:space="preserve">Quote Comparison — Cardiac MVR Suture Skills Kit (3 parts)</t>
   </si>
@@ -62,9 +346,6 @@
 (current)</t>
   </si>
   <si>
-    <t xml:space="preserve">Xometry</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fictiv A2 — SLS
 (newest)</t>
   </si>
@@ -120,9 +401,6 @@
     <t xml:space="preserve">Quantities quoted</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 / 20 / 50</t>
   </si>
   <si>
@@ -132,30 +410,12 @@
     <t xml:space="preserve">*** A1 now quotes 50, so a TRUE like-for-like is finally possible. ***</t>
   </si>
   <si>
-    <t xml:space="preserve">Process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MJF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Both PA12 powder-bed, both vapor smoothed.</t>
   </si>
   <si>
-    <t xml:space="preserve">Material</t>
-  </si>
-  <si>
     <t xml:space="preserve">PA 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Nylon 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nylon (powder)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chemically equivalent.</t>
   </si>
   <si>
@@ -184,9 +444,6 @@
   </si>
   <si>
     <t xml:space="preserve">2) AS-QUOTED UNIT PRICES  ($ per single part)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part</t>
   </si>
   <si>
     <t xml:space="preserve">Volume
@@ -335,24 +592,9 @@
     <t xml:space="preserve">Fictiv re-quoted the same three parts on SLS. The process switch cut its price 21.5% and closed most of the gap to Xometry. Parts only — Fictiv's quote total carries $7,252.29 that Xometry has not quoted.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictiv MJF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fictiv SLS</t>
-  </si>
-  <si>
     <t xml:space="preserve">MJF→SLS</t>
   </si>
   <si>
-    <t xml:space="preserve">Xometry SLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheapest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Why</t>
-  </si>
-  <si>
     <t xml:space="preserve">Small part packs ~117 per MJF build — no envelope penalty, so MJF wins it.</t>
   </si>
   <si>
@@ -362,19 +604,10 @@
     <t xml:space="preserve">Largest part — biggest envelope penalty on MJF, so the biggest SLS gain.</t>
   </si>
   <si>
-    <t xml:space="preserve">KIT (one of each)</t>
-  </si>
-  <si>
     <t xml:space="preserve">TOTAL AT 50 KITS  (parts only)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictiv — MJF (superseded)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fictiv — SLS (newest)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xometry — SLS</t>
   </si>
   <si>
     <t xml:space="preserve">Saved by switching MJF→SLS</t>
@@ -723,18 +956,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="0"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
-    <numFmt numFmtId="170" formatCode="\$#,##0"/>
-    <numFmt numFmtId="171" formatCode="\$#,##0"/>
-    <numFmt numFmtId="172" formatCode="0.00%"/>
+    <numFmt numFmtId="167" formatCode="\+0.0%;\-0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.000"/>
+    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -759,15 +991,15 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
+      <sz val="16"/>
       <color rgb="FF1F4E78"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF808080"/>
+      <sz val="10"/>
+      <color rgb="FF4D5862"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -776,6 +1008,37 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF5C6670"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -797,7 +1060,78 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <color rgb="FF7F6000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF7F6000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF1F4E78"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -813,22 +1147,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
       <color rgb="FF375623"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF008000"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -923,29 +1242,13 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF7F6000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -960,19 +1263,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F6FA"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
         <bgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFEDF5E6"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFEDF5E6"/>
       </patternFill>
     </fill>
@@ -984,8 +1293,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFEDF5E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFEDF5E6"/>
+        <bgColor rgb="FFF2F6FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1044,7 +1359,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="67">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1069,183 +1384,247 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="24" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="24" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="24" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="25" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="25" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="24" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1258,22 +1637,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF006100"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -1328,7 +1692,7 @@
       <rgbColor rgb="FFEDF5E6"/>
       <rgbColor rgb="FFC6EFCE"/>
       <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFF2F6FA"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFC7CE"/>
@@ -1338,12 +1702,12 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFC55A11"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF5C6670"/>
       <rgbColor rgb="FFB3B3B3"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF006100"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF4D5862"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
@@ -1600,11 +1964,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="52827910"/>
-        <c:axId val="78321867"/>
+        <c:axId val="13792238"/>
+        <c:axId val="55572259"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="52827910"/>
+        <c:axId val="13792238"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1669,7 +2033,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78321867"/>
+        <c:crossAx val="55572259"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1677,7 +2041,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78321867"/>
+        <c:axId val="55572259"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1742,7 +2106,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52827910"/>
+        <c:crossAx val="13792238"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1805,9 +2169,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>249480</xdr:colOff>
+      <xdr:colOff>248040</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>46800</xdr:rowOff>
+      <xdr:rowOff>45360</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1816,7 +2180,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="177840" y="5172120"/>
-        <a:ext cx="5938920" cy="3094920"/>
+        <a:ext cx="5937480" cy="3093480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2009,6 +2373,837 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
+  <dimension ref="B2:I51"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="3"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="n">
+        <f aca="false">'Process Comparison @ 50'!C14</f>
+        <v>54540</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6" t="n">
+        <f aca="false">'Process Comparison @ 50'!C16</f>
+        <v>12824</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6" t="n">
+        <f aca="false">'Process Comparison @ 50'!C15</f>
+        <v>18463</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="7" t="n">
+        <v>7252.29</v>
+      </c>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <f aca="false">'Process Comparison @ 50'!C20</f>
+        <v>54246.5</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!C20/QtyKits</f>
+        <v>1084.93</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <f aca="false">E13-MIN($E$13:$E$17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <f aca="false">'Process Comparison @ 50'!C14</f>
+        <v>54540</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!C14/QtyKits</f>
+        <v>1090.8</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <f aca="false">E14-MIN($E$13:$E$17)</f>
+        <v>293.500000000007</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <f aca="false">'Process Comparison @ 50'!C21</f>
+        <v>66453</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!C21/QtyKits</f>
+        <v>1329.06</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <f aca="false">E15-MIN($E$13:$E$17)</f>
+        <v>12206.5</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <f aca="false">'Process Comparison @ 50'!C13</f>
+        <v>67364</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!C13/QtyKits</f>
+        <v>1347.28</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <f aca="false">E16-MIN($E$13:$E$17)</f>
+        <v>13117.5</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <f aca="false">'Process Comparison @ 50'!C12</f>
+        <v>85827</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!C12/QtyKits</f>
+        <v>1716.54</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <f aca="false">E17-MIN($E$13:$E$17)</f>
+        <v>31580.5</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" s="9"/>
+    </row>
+    <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="17" t="str">
+        <f aca="false">'Process Comparison @ 50'!B6</f>
+        <v>667357  Valve receptacle</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!C6</f>
+        <v>53.71</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!D6</f>
+        <v>71.93</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <f aca="false">'Process Comparison @ 50'!E6</f>
+        <v>0.339229193818656</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!F6</f>
+        <v>59.58</v>
+      </c>
+      <c r="G24" s="19" t="str">
+        <f aca="false">'Process Comparison @ 50'!G6</f>
+        <v>Fictiv MJF</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I24" s="16"/>
+    </row>
+    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="17" t="str">
+        <f aca="false">'Process Comparison @ 50'!B7</f>
+        <v>667355  Chest</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!C7</f>
+        <v>616.18</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!D7</f>
+        <v>541.58</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <f aca="false">'Process Comparison @ 50'!E7</f>
+        <v>-0.121068518939271</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!F7</f>
+        <v>378.56</v>
+      </c>
+      <c r="G25" s="19" t="str">
+        <f aca="false">'Process Comparison @ 50'!G7</f>
+        <v>Xometry</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25" s="16"/>
+    </row>
+    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="17" t="str">
+        <f aca="false">'Process Comparison @ 50'!B8</f>
+        <v>667354  Base</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!C8</f>
+        <v>1046.65</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!D8</f>
+        <v>733.77</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <f aca="false">'Process Comparison @ 50'!E8</f>
+        <v>-0.298934696412363</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <f aca="false">'Process Comparison @ 50'!F8</f>
+        <v>652.66</v>
+      </c>
+      <c r="G26" s="19" t="str">
+        <f aca="false">'Process Comparison @ 50'!G8</f>
+        <v>Xometry</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="16"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="20" t="n">
+        <f aca="false">'Process Comparison @ 50'!C9</f>
+        <v>1716.54</v>
+      </c>
+      <c r="D27" s="20" t="n">
+        <f aca="false">'Process Comparison @ 50'!D9</f>
+        <v>1347.28</v>
+      </c>
+      <c r="E27" s="21" t="n">
+        <f aca="false">'Process Comparison @ 50'!E9</f>
+        <v>-0.215118785463782</v>
+      </c>
+      <c r="F27" s="20" t="n">
+        <f aca="false">'Process Comparison @ 50'!F9</f>
+        <v>1090.8</v>
+      </c>
+      <c r="G27" s="22" t="str">
+        <f aca="false">IF(MIN(C27,D27,F27)=C27,"Fictiv MJF",IF(MIN(C27,D27,F27)=D27,"Fictiv SLS","Xometry"))</f>
+        <v>Xometry</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" s="23"/>
+      <c r="G31" s="24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" s="23"/>
+      <c r="G32" s="24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" s="23"/>
+      <c r="G33" s="24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F34" s="23"/>
+      <c r="G34" s="25" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="F35" s="23"/>
+      <c r="G35" s="24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="F36" s="23"/>
+      <c r="G36" s="26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="F37" s="23"/>
+      <c r="G37" s="26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F38" s="23"/>
+      <c r="G38" s="26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="28"/>
+      <c r="E42" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+    </row>
+    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43" s="28"/>
+      <c r="E43" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="D44" s="28"/>
+      <c r="E44" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+    </row>
+    <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D45" s="28"/>
+      <c r="E45" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+    </row>
+    <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="28"/>
+      <c r="E46" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="44">
+    <mergeCell ref="B3:I4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B19:I20"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:I42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:I43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="E45:I45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:I46"/>
+    <mergeCell ref="B49:I51"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E13:E17">
+    <cfRule type="dataBar" priority="2">
+      <dataBar showValue="1" minLength="10" maxLength="90">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="90000"/>
+        <color rgb="FF2E75B6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{69913C2A-5068-4322-9E32-309C635D109D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:F27">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>MIN($C24,$D24,$F24)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;A&amp;RPage &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{69913C2A-5068-4322-9E32-309C635D109D}">
+            <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>90000</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FF2E75B6"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E13:E17</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="B2:J34"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -2017,29 +3212,29 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="58"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>0</v>
+      <c r="B2" s="32" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="B3" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -2050,210 +3245,210 @@
       <c r="I5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5"/>
-      <c r="C6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="B7" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="B8" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="C11" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="F11" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="B12" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="B13" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="B14" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -2264,145 +3459,145 @@
       <c r="I16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>53</v>
+      <c r="B17" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="9" t="n">
+      <c r="B18" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="36" t="n">
         <v>2.56</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="37" t="n">
         <v>168.68</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="37" t="n">
         <v>159.8</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="37" t="n">
         <v>58.54</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="37" t="n">
         <v>53.71</v>
       </c>
-      <c r="H18" s="10" t="n">
+      <c r="H18" s="37" t="n">
         <v>59.58</v>
       </c>
-      <c r="I18" s="11" t="n">
+      <c r="I18" s="37" t="n">
         <v>71.93</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="9" t="n">
+      <c r="B19" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19" s="36" t="n">
         <v>11.952</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="37" t="n">
         <v>1039.11</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="37" t="n">
         <v>984.42</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="37" t="n">
         <v>648.38</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="37" t="n">
         <v>616.18</v>
       </c>
-      <c r="H19" s="10" t="n">
+      <c r="H19" s="37" t="n">
         <v>378.56</v>
       </c>
-      <c r="I19" s="11" t="n">
+      <c r="I19" s="37" t="n">
         <v>541.58</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="9" t="n">
+      <c r="B20" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="36" t="n">
         <v>25.007</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="37" t="n">
         <v>1709.77</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E20" s="37" t="n">
         <v>1619.78</v>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="37" t="n">
         <v>1101.19</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G20" s="37" t="n">
         <v>1046.65</v>
       </c>
-      <c r="H20" s="10" t="n">
+      <c r="H20" s="37" t="n">
         <v>652.66</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I20" s="37" t="n">
         <v>733.77</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="13" t="n">
+      <c r="B21" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" s="39" t="n">
         <f aca="false">SUM(C18:C20)</f>
         <v>39.519</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="40" t="n">
         <f aca="false">SUM(D18:D20)</f>
         <v>2917.56</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="40" t="n">
         <f aca="false">SUM(E18:E20)</f>
         <v>2764</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="F21" s="40" t="n">
         <f aca="false">SUM(F18:F20)</f>
         <v>1808.11</v>
       </c>
-      <c r="G21" s="14" t="n">
+      <c r="G21" s="40" t="n">
         <f aca="false">SUM(G18:G20)</f>
         <v>1716.54</v>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="H21" s="40" t="n">
         <f aca="false">SUM(H18:H20)</f>
         <v>1090.8</v>
       </c>
-      <c r="I21" s="15" t="n">
+      <c r="I21" s="40" t="n">
         <f aca="false">SUM(I18:I20)</f>
         <v>1347.28</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -2413,65 +3608,65 @@
       <c r="I23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="16" t="n">
+      <c r="B25" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="41" t="n">
         <v>20</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="F25" s="41" t="n">
         <v>32</v>
       </c>
-      <c r="G25" s="16" t="n">
+      <c r="G25" s="41" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="B26" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -2482,54 +3677,54 @@
       <c r="I29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="17" t="n">
+      <c r="B30" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="C30" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+      <c r="E30" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
+      <c r="B32" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2556,7 +3751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -2574,186 +3769,186 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>65</v>
+      <c r="B2" s="32" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="B3" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>73</v>
+      <c r="B5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18" t="str">
+      <c r="B6" s="43" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B18</f>
         <v>667357  Valve receptacle</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!G18</f>
         <v>53.71</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!H18</f>
         <v>59.58</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="40" t="n">
         <f aca="false">C6-D6</f>
         <v>-5.87</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="44" t="n">
         <f aca="false">IF(MAX(C6,D6)=0,0,ABS(C6-D6)/MAX(C6,D6))</f>
         <v>0.098522994293387</v>
       </c>
-      <c r="G6" s="20" t="str">
+      <c r="G6" s="45" t="str">
         <f aca="false">IF(C6&lt;D6,"FICTIV","XOMETRY")</f>
         <v>FICTIV</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="40" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!C18=0,0,C6/'Inputs &amp; Assumptions'!C18)</f>
         <v>20.98046875</v>
       </c>
-      <c r="I6" s="14" t="n">
+      <c r="I6" s="40" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!C18=0,0,D6/'Inputs &amp; Assumptions'!C18)</f>
         <v>23.2734375</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="18" t="str">
+      <c r="B7" s="43" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B19</f>
         <v>667355  Chest</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!G19</f>
         <v>616.18</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!H19</f>
         <v>378.56</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="40" t="n">
         <f aca="false">C7-D7</f>
         <v>237.62</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="44" t="n">
         <f aca="false">IF(MAX(C7,D7)=0,0,ABS(C7-D7)/MAX(C7,D7))</f>
         <v>0.385634067967152</v>
       </c>
-      <c r="G7" s="20" t="str">
+      <c r="G7" s="45" t="str">
         <f aca="false">IF(C7&lt;D7,"FICTIV","XOMETRY")</f>
         <v>XOMETRY</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="40" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!C19=0,0,C7/'Inputs &amp; Assumptions'!C19)</f>
         <v>51.5545515394913</v>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="I7" s="40" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!C19=0,0,D7/'Inputs &amp; Assumptions'!C19)</f>
         <v>31.673360107095</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="18" t="str">
+      <c r="B8" s="43" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B20</f>
         <v>667354  Base</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!G20</f>
         <v>1046.65</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!H20</f>
         <v>652.66</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="40" t="n">
         <f aca="false">C8-D8</f>
         <v>393.99</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="44" t="n">
         <f aca="false">IF(MAX(C8,D8)=0,0,ABS(C8-D8)/MAX(C8,D8))</f>
         <v>0.376429560980271</v>
       </c>
-      <c r="G8" s="20" t="str">
+      <c r="G8" s="45" t="str">
         <f aca="false">IF(C8&lt;D8,"FICTIV","XOMETRY")</f>
         <v>XOMETRY</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="40" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!C20=0,0,C8/'Inputs &amp; Assumptions'!C20)</f>
         <v>41.8542808013756</v>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="40" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!C20=0,0,D8/'Inputs &amp; Assumptions'!C20)</f>
         <v>26.0990922541688</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="14" t="n">
+      <c r="B9" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="40" t="n">
         <f aca="false">SUM(C6:C8)</f>
         <v>1716.54</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="40" t="n">
         <f aca="false">SUM(D6:D8)</f>
         <v>1090.8</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="40" t="n">
         <f aca="false">C9-D9</f>
         <v>625.74</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="44" t="n">
         <f aca="false">IF(MAX(C9,D9)=0,0,ABS(C9-D9)/MAX(C9,D9))</f>
         <v>0.364535635639135</v>
       </c>
-      <c r="G9" s="20" t="str">
+      <c r="G9" s="45" t="str">
         <f aca="false">IF(C9&lt;D9,"FICTIV","XOMETRY")</f>
         <v>XOMETRY</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="40" t="n">
         <f aca="false">IF(VolKit=0,0,C9/VolKit)</f>
         <v>43.4358156835952</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="I9" s="40" t="n">
         <f aca="false">IF(VolKit=0,0,D9/VolKit)</f>
         <v>27.6019130038716</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -2763,44 +3958,44 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="21" t="n">
+      <c r="B12" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" s="46" t="n">
         <f aca="false">C9*QtyKits</f>
         <v>85827</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="21" t="n">
+      <c r="B13" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="46" t="n">
         <f aca="false">D9*QtyKits</f>
         <v>54540</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="22" t="n">
+      <c r="B14" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="47" t="n">
         <f aca="false">C12-C13</f>
         <v>31287</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="19" t="n">
+      <c r="B15" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="44" t="n">
         <f aca="false">IF(C12=0,0,(C12-C13)/C12)</f>
         <v>0.364535635639135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -2810,94 +4005,94 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="19" t="n">
+      <c r="B18" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" s="44" t="n">
         <f aca="false">IF(KitA0=0,0,1-KitX50/KitA0)</f>
         <v>0.626125940854687</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="D18" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="19" t="n">
+      <c r="B19" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" s="44" t="n">
         <f aca="false">IF(C9=0,0,1-D9/C9)</f>
         <v>0.364535635639135</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="D19" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" s="19" t="n">
+      <c r="B20" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="44" t="n">
         <f aca="false">IF(KitA1q1=0,0,1-KitA1q50/KitA1q1)</f>
         <v>0.378965267727931</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="D20" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" s="19" t="n">
+      <c r="B21" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="C21" s="44" t="n">
         <f aca="false">IF(KitA1q1=0,0,1-KitX50/KitA1q1)</f>
         <v>0.605354558610709</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="D21" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
+      <c r="B23" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2923,7 +4118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -2931,332 +4126,336 @@
   <dimension ref="B2:H26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="44"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="23" t="s">
-        <v>90</v>
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="32" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="24" t="str">
+      <c r="B3" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="43" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B18</f>
         <v>667357  Valve receptacle</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!G18</f>
         <v>53.71</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!I18</f>
         <v>71.93</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="44" t="n">
         <f aca="false">IF(C6=0,0,D6/C6-1)</f>
         <v>0.339229193818656</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!H18</f>
         <v>59.58</v>
       </c>
-      <c r="G6" s="20" t="str">
+      <c r="G6" s="45" t="str">
         <f aca="false">IF(MIN(C6,D6,F6)=C6,"Fictiv MJF",IF(MIN(C6,D6,F6)=D6,"Fictiv SLS","Xometry"))</f>
         <v>Fictiv MJF</v>
       </c>
-      <c r="H6" s="26" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="24" t="str">
+      <c r="H6" s="48" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="43" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B19</f>
         <v>667355  Chest</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!G19</f>
         <v>616.18</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!I19</f>
         <v>541.58</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="44" t="n">
         <f aca="false">IF(C7=0,0,D7/C7-1)</f>
         <v>-0.121068518939271</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!H19</f>
         <v>378.56</v>
       </c>
-      <c r="G7" s="20" t="str">
+      <c r="G7" s="45" t="str">
         <f aca="false">IF(MIN(C7,D7,F7)=C7,"Fictiv MJF",IF(MIN(C7,D7,F7)=D7,"Fictiv SLS","Xometry"))</f>
         <v>Xometry</v>
       </c>
-      <c r="H7" s="26" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="24" t="str">
+      <c r="H7" s="48" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="43" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B20</f>
         <v>667354  Base</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!G20</f>
         <v>1046.65</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!I20</f>
         <v>733.77</v>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="44" t="n">
         <f aca="false">IF(C8=0,0,D8/C8-1)</f>
         <v>-0.298934696412363</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!H20</f>
         <v>652.66</v>
       </c>
-      <c r="G8" s="20" t="str">
+      <c r="G8" s="45" t="str">
         <f aca="false">IF(MIN(C8,D8,F8)=C8,"Fictiv MJF",IF(MIN(C8,D8,F8)=D8,"Fictiv SLS","Xometry"))</f>
         <v>Xometry</v>
       </c>
-      <c r="H8" s="26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="15" t="n">
+      <c r="H8" s="48" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="40" t="n">
         <f aca="false">SUM(C6:C8)</f>
         <v>1716.54</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="40" t="n">
         <f aca="false">SUM(D6:D8)</f>
         <v>1347.28</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="44" t="n">
         <f aca="false">IF(C9=0,0,D9/C9-1)</f>
         <v>-0.215118785463782</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="40" t="n">
         <f aca="false">SUM(F6:F8)</f>
         <v>1090.8</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="30" t="n">
+      <c r="G9" s="49" t="str">
+        <f aca="false">IF(MIN(C9,D9,F9)=C9,"Fictiv MJF",IF(MIN(C9,D9,F9)=D9,"Fictiv SLS","Xometry"))</f>
+        <v>Xometry</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="46" t="n">
         <f aca="false">C9*QtyKits</f>
         <v>85827</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="30" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="C13" s="46" t="n">
         <f aca="false">D9*QtyKits</f>
         <v>67364</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="30" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="46" t="n">
         <f aca="false">F9*QtyKits</f>
         <v>54540</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="31" t="n">
+      <c r="B15" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="50" t="n">
         <f aca="false">C12-C13</f>
         <v>18463</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="D15" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C16" s="32" t="n">
+      <c r="B16" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C16" s="47" t="n">
         <f aca="false">C13-C14</f>
         <v>12824</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="D16" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="25" t="n">
+      <c r="B17" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="44" t="n">
         <f aca="false">IF(C13=0,0,(C13-C14)/C13)</f>
         <v>0.190368742948756</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
+      <c r="D17" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="30" t="n">
+      <c r="B20" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20" s="46" t="n">
         <f aca="false">(MIN(C6,D6,F6)+MIN(C7,D7,F7)+MIN(C8,D8,F8))*QtyKits</f>
         <v>54246.5</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="D20" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="30" t="n">
+      <c r="B21" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="46" t="n">
         <f aca="false">(MIN(C6,D6)+MIN(C7,D7)+MIN(C8,D8))*QtyKits</f>
         <v>66453</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="D21" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" s="30" t="n">
+      <c r="B22" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" s="46" t="n">
         <f aca="false">F9*QtyKits</f>
         <v>54540</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="D22" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
+      <c r="B24" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3270,7 +4469,7 @@
     <mergeCell ref="B24:H26"/>
   </mergeCells>
   <conditionalFormatting sqref="C6:F9">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>MIN($C6,$D6,$F6)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3284,7 +4483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -3299,142 +4498,142 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>120</v>
+      <c r="B2" s="32" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="B3" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K4" s="33" t="s">
-        <v>122</v>
+      <c r="K4" s="51" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-      <c r="K5" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="L5" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="M5" s="34" t="s">
-        <v>126</v>
+      <c r="K5" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="L5" s="52" t="s">
+        <v>202</v>
+      </c>
+      <c r="M5" s="52" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5"/>
-      <c r="C6" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="K6" s="35" t="n">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="K6" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="36" t="n">
+      <c r="L6" s="54" t="n">
         <f aca="false">KitA1q1</f>
         <v>2764</v>
       </c>
-      <c r="M6" s="36" t="n">
+      <c r="M6" s="54" t="n">
         <f aca="false">KitX50</f>
         <v>1090.8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" s="14" t="n">
+      <c r="B7" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="40" t="n">
         <f aca="false">KitA1q1</f>
         <v>2764</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="40" t="n">
         <f aca="false">KitA1q20</f>
         <v>1808.11</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="40" t="n">
         <f aca="false">KitA1q50</f>
         <v>1716.54</v>
       </c>
-      <c r="K7" s="35" t="n">
+      <c r="K7" s="53" t="n">
         <v>20</v>
       </c>
-      <c r="L7" s="36" t="n">
+      <c r="L7" s="54" t="n">
         <f aca="false">KitA1q20</f>
         <v>1808.11</v>
       </c>
-      <c r="M7" s="36" t="n">
+      <c r="M7" s="54" t="n">
         <f aca="false">KitX50</f>
         <v>1090.8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="E8" s="14" t="n">
+      <c r="B8" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="E8" s="40" t="n">
         <f aca="false">KitX50</f>
         <v>1090.8</v>
       </c>
-      <c r="K8" s="35" t="n">
+      <c r="K8" s="53" t="n">
         <v>50</v>
       </c>
-      <c r="L8" s="36" t="n">
+      <c r="L8" s="54" t="n">
         <f aca="false">KitA1q50</f>
         <v>1716.54</v>
       </c>
-      <c r="M8" s="36" t="n">
+      <c r="M8" s="54" t="n">
         <f aca="false">KitX50</f>
         <v>1090.8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="E9" s="19" t="n">
+      <c r="B9" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="E9" s="44" t="n">
         <f aca="false">IF(KitX50=0,0,KitA1q50/KitX50-1)</f>
         <v>0.573652365236524</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -3443,115 +4642,115 @@
       <c r="G11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="B12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="18" t="str">
+      <c r="B13" s="43" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B18</f>
         <v>667357  Valve receptacle</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="44" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!E18=0,0,'Inputs &amp; Assumptions'!F18/'Inputs &amp; Assumptions'!E18-1)</f>
         <v>-0.633667083854819</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="44" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!F18=0,0,'Inputs &amp; Assumptions'!G18/'Inputs &amp; Assumptions'!F18-1)</f>
         <v>-0.0825076870515886</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="44" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!E18=0,0,'Inputs &amp; Assumptions'!G18/'Inputs &amp; Assumptions'!E18-1)</f>
         <v>-0.663892365456821</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="18" t="str">
+      <c r="B14" s="43" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B19</f>
         <v>667355  Chest</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="44" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!E19=0,0,'Inputs &amp; Assumptions'!F19/'Inputs &amp; Assumptions'!E19-1)</f>
         <v>-0.341358363300217</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="44" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!F19=0,0,'Inputs &amp; Assumptions'!G19/'Inputs &amp; Assumptions'!F19-1)</f>
         <v>-0.0496622351090411</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="44" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!E19=0,0,'Inputs &amp; Assumptions'!G19/'Inputs &amp; Assumptions'!E19-1)</f>
         <v>-0.374067979114606</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="18" t="str">
+      <c r="B15" s="43" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B20</f>
         <v>667354  Base</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="44" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!E20=0,0,'Inputs &amp; Assumptions'!F20/'Inputs &amp; Assumptions'!E20-1)</f>
         <v>-0.320160762572695</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="44" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!F20=0,0,'Inputs &amp; Assumptions'!G20/'Inputs &amp; Assumptions'!F20-1)</f>
         <v>-0.0495282376338324</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="44" t="n">
         <f aca="false">IF('Inputs &amp; Assumptions'!E20=0,0,'Inputs &amp; Assumptions'!G20/'Inputs &amp; Assumptions'!E20-1)</f>
         <v>-0.353832001876798</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="C16" s="19" t="n">
+      <c r="B16" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="C16" s="44" t="n">
         <f aca="false">IF(KitA1q1=0,0,KitA1q20/KitA1q1-1)</f>
         <v>-0.345835745296672</v>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="44" t="n">
         <f aca="false">IF(KitA1q20=0,0,KitA1q50/KitA1q20-1)</f>
         <v>-0.0506440426743949</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="44" t="n">
         <f aca="false">IF(KitA1q1=0,0,KitA1q50/KitA1q1-1)</f>
         <v>-0.378965267727931</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
+      <c r="B18" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -3560,46 +4759,46 @@
       <c r="G21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C22" s="14" t="n">
+      <c r="B22" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="C22" s="40" t="n">
         <f aca="false">KitA1q50</f>
         <v>1716.54</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C23" s="14" t="n">
+      <c r="B23" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="C23" s="40" t="n">
         <f aca="false">KitX50</f>
         <v>1090.8</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C24" s="38" t="n">
+      <c r="B24" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" s="56" t="n">
         <f aca="false">IF(KitA1q50=0,0,1-KitX50/KitA1q50)</f>
         <v>0.364535635639135</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C25" s="14" t="n">
+      <c r="B25" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="C25" s="40" t="n">
         <f aca="false">KitA1q50-KitX50</f>
         <v>625.74</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C26" s="21" t="n">
+      <c r="B26" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="C26" s="46" t="n">
         <f aca="false">(KitA1q50-KitX50)*QtyKits</f>
         <v>31287</v>
       </c>
@@ -3620,7 +4819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -3637,136 +4836,136 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>146</v>
+      <c r="B2" s="32" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="B3" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="H5" s="5"/>
+      <c r="B5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18" t="str">
+      <c r="B6" s="43" t="str">
         <f aca="false">'Head-to-Head @ 50'!B6</f>
         <v>667357  Valve receptacle</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="40" t="n">
         <f aca="false">'Head-to-Head @ 50'!C6</f>
         <v>53.71</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="40" t="n">
         <f aca="false">'Head-to-Head @ 50'!D6</f>
         <v>59.58</v>
       </c>
-      <c r="E6" s="20" t="str">
+      <c r="E6" s="45" t="str">
         <f aca="false">IF(C6&lt;D6,"FICTIV","XOMETRY")</f>
         <v>FICTIV</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="40" t="n">
         <f aca="false">MIN(C6,D6)</f>
         <v>53.71</v>
       </c>
-      <c r="G6" s="21" t="n">
+      <c r="G6" s="46" t="n">
         <f aca="false">F6*QtyKits</f>
         <v>2685.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="18" t="str">
+      <c r="B7" s="43" t="str">
         <f aca="false">'Head-to-Head @ 50'!B7</f>
         <v>667355  Chest</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="40" t="n">
         <f aca="false">'Head-to-Head @ 50'!C7</f>
         <v>616.18</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="40" t="n">
         <f aca="false">'Head-to-Head @ 50'!D7</f>
         <v>378.56</v>
       </c>
-      <c r="E7" s="20" t="str">
+      <c r="E7" s="45" t="str">
         <f aca="false">IF(C7&lt;D7,"FICTIV","XOMETRY")</f>
         <v>XOMETRY</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="40" t="n">
         <f aca="false">MIN(C7,D7)</f>
         <v>378.56</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="46" t="n">
         <f aca="false">F7*QtyKits</f>
         <v>18928</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="18" t="str">
+      <c r="B8" s="43" t="str">
         <f aca="false">'Head-to-Head @ 50'!B8</f>
         <v>667354  Base</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="40" t="n">
         <f aca="false">'Head-to-Head @ 50'!C8</f>
         <v>1046.65</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="40" t="n">
         <f aca="false">'Head-to-Head @ 50'!D8</f>
         <v>652.66</v>
       </c>
-      <c r="E8" s="20" t="str">
+      <c r="E8" s="45" t="str">
         <f aca="false">IF(C8&lt;D8,"FICTIV","XOMETRY")</f>
         <v>XOMETRY</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="40" t="n">
         <f aca="false">MIN(C8,D8)</f>
         <v>652.66</v>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="G8" s="46" t="n">
         <f aca="false">F8*QtyKits</f>
         <v>32633</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="F9" s="14" t="n">
+      <c r="B9" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="F9" s="40" t="n">
         <f aca="false">SUM(F6:F8)</f>
         <v>1084.93</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="46" t="n">
         <f aca="false">SUM(G6:G8)</f>
         <v>54246.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>154</v>
+        <v>231</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -3775,108 +4974,108 @@
       <c r="G11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C12" s="21" t="n">
+      <c r="B12" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" s="46" t="n">
         <f aca="false">KitX50*QtyKits</f>
         <v>54540</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" s="21" t="n">
+      <c r="B13" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="C13" s="46" t="n">
         <f aca="false">KitA1q50*QtyKits</f>
         <v>85827</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C14" s="21" t="n">
+      <c r="B14" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" s="46" t="n">
         <f aca="false">G9</f>
         <v>54246.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C15" s="39" t="n">
+      <c r="B15" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="C15" s="57" t="n">
         <f aca="false">C12-C14</f>
         <v>293.5</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="D15" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C16" s="19" t="n">
+      <c r="B16" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="C16" s="44" t="n">
         <f aca="false">IF(C12=0,0,(C12-C14)/C12)</f>
         <v>0.00538137147048038</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="D16" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C17" s="21" t="n">
+      <c r="B17" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="C17" s="46" t="n">
         <f aca="false">C13-C14</f>
         <v>31580.5</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="D17" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
+      <c r="B19" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3901,7 +5100,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -3917,128 +5116,128 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>165</v>
+      <c r="B2" s="32" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="B3" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="G5" s="5"/>
+      <c r="B5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18" t="str">
+      <c r="B6" s="43" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B18</f>
         <v>667357  Valve receptacle</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!D18</f>
         <v>168.68</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!E18</f>
         <v>159.8</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="40" t="n">
         <f aca="false">D6-C6</f>
         <v>-8.88</v>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="58" t="n">
         <f aca="false">IF(C6=0,0,D6/C6-1)</f>
         <v>-0.0526440597581218</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="18" t="str">
+      <c r="B7" s="43" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B19</f>
         <v>667355  Chest</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!D19</f>
         <v>1039.11</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!E19</f>
         <v>984.42</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="40" t="n">
         <f aca="false">D7-C7</f>
         <v>-54.6899999999999</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="58" t="n">
         <f aca="false">IF(C7=0,0,D7/C7-1)</f>
         <v>-0.0526315789473684</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="18" t="str">
+      <c r="B8" s="43" t="str">
         <f aca="false">'Inputs &amp; Assumptions'!B20</f>
         <v>667354  Base</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!D20</f>
         <v>1709.77</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="40" t="n">
         <f aca="false">'Inputs &amp; Assumptions'!E20</f>
         <v>1619.78</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="40" t="n">
         <f aca="false">D8-C8</f>
         <v>-89.99</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="58" t="n">
         <f aca="false">IF(C8=0,0,D8/C8-1)</f>
         <v>-0.0526328102610293</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="14" t="n">
+      <c r="B9" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" s="40" t="n">
         <f aca="false">SUM(C6:C8)</f>
         <v>2917.56</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="40" t="n">
         <f aca="false">SUM(D6:D8)</f>
         <v>2764</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="40" t="n">
         <f aca="false">D9-C9</f>
         <v>-153.56</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="58" t="n">
         <f aca="false">IF(C9=0,0,D9/C9-1)</f>
         <v>-0.0526330221143695</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>171</v>
+        <v>248</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -4046,40 +5245,40 @@
       <c r="F11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>173</v>
-      </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="59" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" s="60" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="41" t="s">
-        <v>174</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
+      <c r="B13" s="59" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" s="60" t="s">
+        <v>252</v>
+      </c>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
+      <c r="B14" s="59" t="s">
+        <v>253</v>
+      </c>
+      <c r="C14" s="60" t="s">
+        <v>254</v>
+      </c>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4098,7 +5297,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -4113,199 +5312,199 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>178</v>
+      <c r="B2" s="32" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>180</v>
+        <v>257</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="D6" s="43"/>
+      <c r="B6" s="59" t="s">
+        <v>258</v>
+      </c>
+      <c r="C6" s="61" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="61"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="41" t="s">
-        <v>183</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="43"/>
+      <c r="B7" s="59" t="s">
+        <v>260</v>
+      </c>
+      <c r="C7" s="61" t="s">
+        <v>261</v>
+      </c>
+      <c r="D7" s="61"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="D8" s="43"/>
+      <c r="B8" s="59" t="s">
+        <v>262</v>
+      </c>
+      <c r="C8" s="61" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="61"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="41" t="s">
-        <v>187</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="D9" s="43"/>
+      <c r="B9" s="59" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="61" t="s">
+        <v>265</v>
+      </c>
+      <c r="D9" s="61"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="D10" s="43"/>
+      <c r="B10" s="59" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" s="61"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="41" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="43"/>
+      <c r="B11" s="59" t="s">
+        <v>268</v>
+      </c>
+      <c r="C11" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="D11" s="61"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>195</v>
+      <c r="B13" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="44" t="s">
-        <v>196</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="D14" s="46" t="s">
-        <v>198</v>
+      <c r="B14" s="62" t="s">
+        <v>273</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>274</v>
+      </c>
+      <c r="D14" s="64" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="44" t="s">
-        <v>199</v>
-      </c>
-      <c r="C15" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>201</v>
+      <c r="B15" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="C15" s="63" t="s">
+        <v>277</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="44" t="s">
-        <v>202</v>
-      </c>
-      <c r="C16" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="D16" s="48" t="s">
-        <v>204</v>
+      <c r="B16" s="62" t="s">
+        <v>279</v>
+      </c>
+      <c r="C16" s="63" t="s">
+        <v>280</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="44" t="s">
-        <v>205</v>
-      </c>
-      <c r="C17" s="45" t="s">
-        <v>206</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>207</v>
+      <c r="B17" s="62" t="s">
+        <v>282</v>
+      </c>
+      <c r="C17" s="63" t="s">
+        <v>283</v>
+      </c>
+      <c r="D17" s="65" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="44" t="s">
-        <v>208</v>
-      </c>
-      <c r="C18" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="D18" s="50" t="s">
-        <v>210</v>
+      <c r="B18" s="62" t="s">
+        <v>285</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="D18" s="66" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="44" t="s">
-        <v>211</v>
-      </c>
-      <c r="C19" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="D19" s="46" t="s">
-        <v>198</v>
+      <c r="B19" s="62" t="s">
+        <v>288</v>
+      </c>
+      <c r="C19" s="63" t="s">
+        <v>289</v>
+      </c>
+      <c r="D19" s="64" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="44" t="s">
-        <v>213</v>
-      </c>
-      <c r="C20" s="45" t="s">
-        <v>214</v>
-      </c>
-      <c r="D20" s="46" t="s">
-        <v>198</v>
+      <c r="B20" s="62" t="s">
+        <v>290</v>
+      </c>
+      <c r="C20" s="63" t="s">
+        <v>291</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="44" t="s">
-        <v>215</v>
-      </c>
-      <c r="C21" s="45" t="s">
-        <v>216</v>
-      </c>
-      <c r="D21" s="49" t="s">
-        <v>207</v>
+      <c r="B21" s="62" t="s">
+        <v>292</v>
+      </c>
+      <c r="C21" s="63" t="s">
+        <v>293</v>
+      </c>
+      <c r="D21" s="65" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="44" t="s">
-        <v>217</v>
-      </c>
-      <c r="C22" s="45" t="s">
-        <v>218</v>
-      </c>
-      <c r="D22" s="49" t="s">
-        <v>207</v>
+      <c r="B22" s="62" t="s">
+        <v>294</v>
+      </c>
+      <c r="C22" s="63" t="s">
+        <v>295</v>
+      </c>
+      <c r="D22" s="65" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="B24" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">
